--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.20153926881233</v>
+        <v>25.27585784259344</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.15655280142654</v>
+        <v>26.24495738787133</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.24652573619812</v>
+        <v>24.30675829731555</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.14408770910235</v>
+        <v>1.144107553411272</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18725.77610600724</v>
+        <v>18314.40686090312</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7511146735854168</v>
+        <v>0.7357204180880825</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>925.5002448642541</v>
+        <v>923.9677068999425</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500.169228354622</v>
+        <v>505.6279220333513</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1161.644473218876</v>
+        <v>1165.570628933294</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26.15655280142654</v>
+        <v>26.24495738787133</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.15655280142654</v>
+        <v>26.24495738787133</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.029237964349</v>
+        <v>22.10541218721925</v>
       </c>
       <c r="F11" t="n">
-        <v>17.41898206586427</v>
+        <v>17.4792146269817</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.24652573619812</v>
+        <v>24.30675829731555</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.33109630035358</v>
+        <v>18.39055115937847</v>
       </c>
       <c r="C2" t="n">
-        <v>21.04216544937606</v>
+        <v>21.10905216577906</v>
       </c>
       <c r="D2" t="n">
-        <v>23.75323459839855</v>
+        <v>23.82755317217966</v>
       </c>
       <c r="E2" t="n">
-        <v>26.46430374742103</v>
+        <v>26.54605417858026</v>
       </c>
       <c r="F2" t="n">
-        <v>29.1753728964435</v>
+        <v>29.26455518498086</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.05524863556047</v>
+        <v>19.11470349458536</v>
       </c>
       <c r="C3" t="n">
-        <v>21.76631778458295</v>
+        <v>21.83320450098595</v>
       </c>
       <c r="D3" t="n">
-        <v>24.47738693360544</v>
+        <v>24.55170550738655</v>
       </c>
       <c r="E3" t="n">
-        <v>27.18845608262793</v>
+        <v>27.27020651378715</v>
       </c>
       <c r="F3" t="n">
-        <v>29.89952523165039</v>
+        <v>29.98870752018775</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.77940097076736</v>
+        <v>19.83885582979226</v>
       </c>
       <c r="C4" t="n">
-        <v>22.49047011978984</v>
+        <v>22.55735683619285</v>
       </c>
       <c r="D4" t="n">
-        <v>25.20153926881233</v>
+        <v>25.27585784259344</v>
       </c>
       <c r="E4" t="n">
-        <v>27.91260841783482</v>
+        <v>27.99435884899404</v>
       </c>
       <c r="F4" t="n">
-        <v>30.62367756685729</v>
+        <v>30.71285985539465</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.50355330597425</v>
+        <v>20.56300816499915</v>
       </c>
       <c r="C5" t="n">
-        <v>23.21462245499674</v>
+        <v>23.28150917139974</v>
       </c>
       <c r="D5" t="n">
-        <v>25.92569160401922</v>
+        <v>26.00001017780033</v>
       </c>
       <c r="E5" t="n">
-        <v>28.63676075304171</v>
+        <v>28.71851118420093</v>
       </c>
       <c r="F5" t="n">
-        <v>31.34782990206418</v>
+        <v>31.43701219060154</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.22770564118115</v>
+        <v>21.28716050020604</v>
       </c>
       <c r="C6" t="n">
-        <v>23.93877479020363</v>
+        <v>24.00566150660663</v>
       </c>
       <c r="D6" t="n">
-        <v>26.64984393922612</v>
+        <v>26.72416251300723</v>
       </c>
       <c r="E6" t="n">
-        <v>29.36091308824861</v>
+        <v>29.44266351940783</v>
       </c>
       <c r="F6" t="n">
-        <v>32.07198223727107</v>
+        <v>32.16116452580843</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.52</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.03</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.2</v>
+        <v>25.28</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18314.40686090312</v>
+        <v>15736.23789208539</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7357204180880825</v>
+        <v>0.6321510496642795</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.5</v>
+        <v>23.805</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15736.23789208539</v>
+        <v>17308.92096306421</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6321510496642795</v>
+        <v>0.6953283644027994</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.805</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17308.92096306421</v>
+        <v>16715.94210023615</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6953283644027994</v>
+        <v>0.6715074096653255</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.27585784259344</v>
+        <v>25.29904327312664</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.24495738787133</v>
+        <v>26.27176128710875</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.30675829731555</v>
+        <v>24.32632525914453</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.144107553411272</v>
+        <v>1.144111291183328</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16715.94210023615</v>
+        <v>16591.68258848124</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6715074096653255</v>
+        <v>0.6667048088714105</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>505.6279220333513</v>
+        <v>506.8183159528501</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1165.570628933294</v>
+        <v>1166.761022852792</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26.24495738787133</v>
+        <v>26.27176128710875</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.24495738787133</v>
+        <v>26.27176128710875</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.10541218721925</v>
+        <v>22.13015790753402</v>
       </c>
       <c r="F11" t="n">
-        <v>17.4792146269817</v>
+        <v>17.49878158881068</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.30675829731555</v>
+        <v>24.32632525914453</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.39055115937847</v>
+        <v>18.40909950380503</v>
       </c>
       <c r="C2" t="n">
-        <v>21.10905216577906</v>
+        <v>21.12991905325894</v>
       </c>
       <c r="D2" t="n">
-        <v>23.82755317217966</v>
+        <v>23.85073860271285</v>
       </c>
       <c r="E2" t="n">
-        <v>26.54605417858026</v>
+        <v>26.57155815216677</v>
       </c>
       <c r="F2" t="n">
-        <v>29.26455518498086</v>
+        <v>29.29237770162069</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.11470349458536</v>
+        <v>19.13325183901192</v>
       </c>
       <c r="C3" t="n">
-        <v>21.83320450098595</v>
+        <v>21.85407138846583</v>
       </c>
       <c r="D3" t="n">
-        <v>24.55170550738655</v>
+        <v>24.57489093791975</v>
       </c>
       <c r="E3" t="n">
-        <v>27.27020651378715</v>
+        <v>27.29571048737366</v>
       </c>
       <c r="F3" t="n">
-        <v>29.98870752018775</v>
+        <v>30.01653003682759</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.83885582979226</v>
+        <v>19.85740417421881</v>
       </c>
       <c r="C4" t="n">
-        <v>22.55735683619285</v>
+        <v>22.57822372367273</v>
       </c>
       <c r="D4" t="n">
-        <v>25.27585784259344</v>
+        <v>25.29904327312664</v>
       </c>
       <c r="E4" t="n">
-        <v>27.99435884899404</v>
+        <v>28.01986282258056</v>
       </c>
       <c r="F4" t="n">
-        <v>30.71285985539465</v>
+        <v>30.74068237203448</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.56300816499915</v>
+        <v>20.58155650942571</v>
       </c>
       <c r="C5" t="n">
-        <v>23.28150917139974</v>
+        <v>23.30237605887962</v>
       </c>
       <c r="D5" t="n">
-        <v>26.00001017780033</v>
+        <v>26.02319560833353</v>
       </c>
       <c r="E5" t="n">
-        <v>28.71851118420093</v>
+        <v>28.74401515778745</v>
       </c>
       <c r="F5" t="n">
-        <v>31.43701219060154</v>
+        <v>31.46483470724137</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.28716050020604</v>
+        <v>21.3057088446326</v>
       </c>
       <c r="C6" t="n">
-        <v>24.00566150660663</v>
+        <v>24.02652839408651</v>
       </c>
       <c r="D6" t="n">
-        <v>26.72416251300723</v>
+        <v>26.74734794354043</v>
       </c>
       <c r="E6" t="n">
-        <v>29.44266351940783</v>
+        <v>29.46816749299434</v>
       </c>
       <c r="F6" t="n">
-        <v>32.16116452580843</v>
+        <v>32.18898704244827</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.59</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.11</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.28</v>
+        <v>25.3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.69</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16591.68258848124</v>
+        <v>16540.13383515256</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6667048088714105</v>
+        <v>0.6646334215029337</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.62</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.13</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.68</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16540.13383515256</v>
+        <v>15973.0975485373</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6646334215029337</v>
+        <v>0.6418481604496973</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.29904327312664</v>
+        <v>23.96485112822545</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.27176128710875</v>
+        <v>24.6402711190527</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.32632525914453</v>
+        <v>23.28943113739819</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.144111291183328</v>
+        <v>1.144228859174459</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15973.0975485373</v>
+        <v>22646.76015935531</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6418481604496973</v>
+        <v>0.9182110360565288</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>923.9677068999425</v>
+        <v>854.2028010894207</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>506.8183159528501</v>
+        <v>504.1267497190173</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1166.761022852792</v>
+        <v>1094.304550808438</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26.27176128710875</v>
+        <v>24.6402711190527</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.27176128710875</v>
+        <v>24.6402711190527</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.13015790753402</v>
+        <v>20.81883057133176</v>
       </c>
       <c r="F11" t="n">
-        <v>17.49878158881068</v>
+        <v>16.46188746706434</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.32632525914453</v>
+        <v>23.28943113739819</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.40909950380503</v>
+        <v>17.34174578788407</v>
       </c>
       <c r="C2" t="n">
-        <v>21.12991905325894</v>
+        <v>19.92914612284786</v>
       </c>
       <c r="D2" t="n">
-        <v>23.85073860271285</v>
+        <v>22.51654645781166</v>
       </c>
       <c r="E2" t="n">
-        <v>26.57155815216677</v>
+        <v>25.10394679277546</v>
       </c>
       <c r="F2" t="n">
-        <v>29.29237770162069</v>
+        <v>27.69134712773926</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.13325183901192</v>
+        <v>18.06589812309096</v>
       </c>
       <c r="C3" t="n">
-        <v>21.85407138846583</v>
+        <v>20.65329845805476</v>
       </c>
       <c r="D3" t="n">
-        <v>24.57489093791975</v>
+        <v>23.24069879301855</v>
       </c>
       <c r="E3" t="n">
-        <v>27.29571048737366</v>
+        <v>25.82809912798235</v>
       </c>
       <c r="F3" t="n">
-        <v>30.01653003682759</v>
+        <v>28.41549946294615</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.85740417421881</v>
+        <v>18.79005045829786</v>
       </c>
       <c r="C4" t="n">
-        <v>22.57822372367273</v>
+        <v>21.37745079326165</v>
       </c>
       <c r="D4" t="n">
-        <v>25.29904327312664</v>
+        <v>23.96485112822545</v>
       </c>
       <c r="E4" t="n">
-        <v>28.01986282258056</v>
+        <v>26.55225146318924</v>
       </c>
       <c r="F4" t="n">
-        <v>30.74068237203448</v>
+        <v>29.13965179815305</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.58155650942571</v>
+        <v>19.51420279350475</v>
       </c>
       <c r="C5" t="n">
-        <v>23.30237605887962</v>
+        <v>22.10160312846854</v>
       </c>
       <c r="D5" t="n">
-        <v>26.02319560833353</v>
+        <v>24.68900346343234</v>
       </c>
       <c r="E5" t="n">
-        <v>28.74401515778745</v>
+        <v>27.27640379839614</v>
       </c>
       <c r="F5" t="n">
-        <v>31.46483470724137</v>
+        <v>29.86380413335994</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.3057088446326</v>
+        <v>20.23835512871164</v>
       </c>
       <c r="C6" t="n">
-        <v>24.02652839408651</v>
+        <v>22.82575546367543</v>
       </c>
       <c r="D6" t="n">
-        <v>26.74734794354043</v>
+        <v>25.41315579863923</v>
       </c>
       <c r="E6" t="n">
-        <v>29.46816749299434</v>
+        <v>28.00055613360303</v>
       </c>
       <c r="F6" t="n">
-        <v>32.18898704244827</v>
+        <v>30.58795646856683</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.22</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.28</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.3</v>
+        <v>23.96</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.96485112822545</v>
+        <v>23.98906580139536</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.6402711190527</v>
+        <v>24.68870046539253</v>
       </c>
     </row>
     <row r="8">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.144228859174459</v>
+        <v>1.144235769812044</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22646.76015935531</v>
+        <v>22511.12892781925</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9182110360565288</v>
+        <v>0.9131952392429352</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>504.1267497190173</v>
+        <v>506.2775561706302</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1094.304550808438</v>
+        <v>1096.455357260051</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.6402711190527</v>
+        <v>24.68870046539253</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.6402711190527</v>
+        <v>24.68870046539253</v>
       </c>
     </row>
     <row r="14">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.34174578788407</v>
+        <v>17.36111752642</v>
       </c>
       <c r="C2" t="n">
-        <v>19.92914612284786</v>
+        <v>19.95093932870078</v>
       </c>
       <c r="D2" t="n">
-        <v>22.51654645781166</v>
+        <v>22.54076113098157</v>
       </c>
       <c r="E2" t="n">
-        <v>25.10394679277546</v>
+        <v>25.13058293326236</v>
       </c>
       <c r="F2" t="n">
-        <v>27.69134712773926</v>
+        <v>27.72040473554316</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.06589812309096</v>
+        <v>18.08526986162689</v>
       </c>
       <c r="C3" t="n">
-        <v>20.65329845805476</v>
+        <v>20.67509166390768</v>
       </c>
       <c r="D3" t="n">
-        <v>23.24069879301855</v>
+        <v>23.26491346618847</v>
       </c>
       <c r="E3" t="n">
-        <v>25.82809912798235</v>
+        <v>25.85473526846926</v>
       </c>
       <c r="F3" t="n">
-        <v>28.41549946294615</v>
+        <v>28.44455707075005</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.79005045829786</v>
+        <v>18.80942219683379</v>
       </c>
       <c r="C4" t="n">
-        <v>21.37745079326165</v>
+        <v>21.39924399911457</v>
       </c>
       <c r="D4" t="n">
-        <v>23.96485112822545</v>
+        <v>23.98906580139536</v>
       </c>
       <c r="E4" t="n">
-        <v>26.55225146318924</v>
+        <v>26.57888760367615</v>
       </c>
       <c r="F4" t="n">
-        <v>29.13965179815305</v>
+        <v>29.16870940595695</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.51420279350475</v>
+        <v>19.53357453204068</v>
       </c>
       <c r="C5" t="n">
-        <v>22.10160312846854</v>
+        <v>22.12339633432146</v>
       </c>
       <c r="D5" t="n">
-        <v>24.68900346343234</v>
+        <v>24.71321813660225</v>
       </c>
       <c r="E5" t="n">
-        <v>27.27640379839614</v>
+        <v>27.30303993888304</v>
       </c>
       <c r="F5" t="n">
-        <v>29.86380413335994</v>
+        <v>29.89286174116384</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.23835512871164</v>
+        <v>20.25772686724757</v>
       </c>
       <c r="C6" t="n">
-        <v>22.82575546367543</v>
+        <v>22.84754866952836</v>
       </c>
       <c r="D6" t="n">
-        <v>25.41315579863923</v>
+        <v>25.43737047180915</v>
       </c>
       <c r="E6" t="n">
-        <v>28.00055613360303</v>
+        <v>28.02719227408993</v>
       </c>
       <c r="F6" t="n">
-        <v>30.58795646856683</v>
+        <v>30.61701407637073</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>23.88</v>
+        <v>23.91</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>23.94</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>23.96</v>
+        <v>23.99</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.57</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22511.12892781925</v>
+        <v>26698.18534336734</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9131952392429352</v>
+        <v>1.083049003457972</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1250,35 +1249,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.39</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26698.18534336734</v>
+        <v>28689.59022393291</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.083049003457972</v>
+        <v>1.163833110828539</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.78</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28689.59022393291</v>
+        <v>28076.85026068197</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.163833110828539</v>
+        <v>1.138976462406826</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.98906580139536</v>
+        <v>23.8458319559573</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.28943113739819</v>
+        <v>22.58152919180447</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27000</v>
+        <v>33100</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29537.5</v>
+        <v>31037.5</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.144235769812044</v>
+        <v>1.356938061630981</v>
       </c>
     </row>
     <row r="12">
@@ -552,7 +552,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>elevated</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28076.85026068197</v>
+        <v>30712.26878601086</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.138976462406826</v>
+        <v>1.203428111982207</v>
       </c>
     </row>
   </sheetData>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31200</v>
+        <v>32500</v>
       </c>
       <c r="C2" t="n">
-        <v>31465</v>
+        <v>32700</v>
       </c>
       <c r="D2" t="n">
-        <v>1.198063771471994</v>
+        <v>1.232626660216645</v>
       </c>
       <c r="E2" t="n">
-        <v>1.198063771471994</v>
+        <v>1.232626660216645</v>
       </c>
       <c r="F2" t="n">
-        <v>1.167210513988501</v>
+        <v>1.200883318472862</v>
       </c>
     </row>
     <row r="3">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31450</v>
+        <v>33650</v>
       </c>
       <c r="C3" t="n">
-        <v>31702.5</v>
+        <v>33792.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.170301707471594</v>
+        <v>1.244219775972388</v>
       </c>
       <c r="E3" t="n">
-        <v>1.170301707471594</v>
+        <v>1.244219775972388</v>
       </c>
       <c r="F3" t="n">
-        <v>1.110801223089465</v>
+        <v>1.180961148837576</v>
       </c>
     </row>
     <row r="4">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28500</v>
+        <v>29500</v>
       </c>
       <c r="C4" t="n">
-        <v>28900</v>
+        <v>29850</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9966365314154156</v>
+        <v>1.032981427531987</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9966365314154156</v>
+        <v>1.032981427531987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9216044603581709</v>
+        <v>0.9552131204026875</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="C5" t="n">
-        <v>27475</v>
+        <v>28900</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9276215001469673</v>
+        <v>0.9821388443218247</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9276215001469673</v>
+        <v>0.9821388443218247</v>
       </c>
       <c r="F5" t="n">
-        <v>0.835695045177448</v>
+        <v>0.8848097696593015</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25500</v>
+        <v>27500</v>
       </c>
       <c r="C6" t="n">
-        <v>26050</v>
+        <v>27950</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8634390312430493</v>
+        <v>0.9312962611116623</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8634390312430493</v>
+        <v>0.9312962611116623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7578407486100324</v>
+        <v>0.8173990636982428</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25000</v>
+        <v>26500</v>
       </c>
       <c r="C7" t="n">
-        <v>25575</v>
+        <v>27000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8380177396379681</v>
+        <v>0.8804536779014998</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8380177396379681</v>
+        <v>0.8804536779014998</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7165867010448768</v>
+        <v>0.7528735569999132</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24500</v>
+        <v>26000</v>
       </c>
       <c r="C8" t="n">
-        <v>25100</v>
+        <v>26525</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8125964480328868</v>
+        <v>0.8550323862964185</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8125964480328868</v>
+        <v>0.8550323862964185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6769548542035975</v>
+        <v>0.7123072292597821</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="C9" t="n">
-        <v>24625</v>
+        <v>26050</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7895914376100707</v>
+        <v>0.8296110946913372</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7895914376100707</v>
+        <v>0.8296110946913372</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6408501238617568</v>
+        <v>0.673330975319647</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.827543670333849</v>
+        <v>7.177778182650012</v>
       </c>
     </row>
     <row r="11">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.81883057133176</v>
+        <v>19.48063872166389</v>
       </c>
       <c r="F11" t="n">
-        <v>16.46188746706434</v>
+        <v>15.40375100915445</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23.28943113739819</v>
+        <v>22.58152919180447</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29537.5</v>
+        <v>31037.5</v>
       </c>
     </row>
   </sheetData>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.36111752642</v>
+        <v>17.36074783563515</v>
       </c>
       <c r="C2" t="n">
-        <v>19.95093932870078</v>
+        <v>20.00295395689174</v>
       </c>
       <c r="D2" t="n">
-        <v>22.54076113098157</v>
+        <v>22.64516007814833</v>
       </c>
       <c r="E2" t="n">
-        <v>25.13058293326236</v>
+        <v>25.28736619940493</v>
       </c>
       <c r="F2" t="n">
-        <v>27.72040473554316</v>
+        <v>27.92957232066153</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.08526986162689</v>
+        <v>17.96108377453963</v>
       </c>
       <c r="C3" t="n">
-        <v>20.67509166390768</v>
+        <v>20.60328989579622</v>
       </c>
       <c r="D3" t="n">
-        <v>23.26491346618847</v>
+        <v>23.24549601705282</v>
       </c>
       <c r="E3" t="n">
-        <v>25.85473526846926</v>
+        <v>25.88770213830941</v>
       </c>
       <c r="F3" t="n">
-        <v>28.44455707075005</v>
+        <v>28.52990825956602</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.80942219683379</v>
+        <v>18.56141971344412</v>
       </c>
       <c r="C4" t="n">
-        <v>21.39924399911457</v>
+        <v>21.20362583470071</v>
       </c>
       <c r="D4" t="n">
-        <v>23.98906580139536</v>
+        <v>23.8458319559573</v>
       </c>
       <c r="E4" t="n">
-        <v>26.57888760367615</v>
+        <v>26.4880380772139</v>
       </c>
       <c r="F4" t="n">
-        <v>29.16870940595695</v>
+        <v>29.1302441984705</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.53357453204068</v>
+        <v>19.1617556523486</v>
       </c>
       <c r="C5" t="n">
-        <v>22.12339633432146</v>
+        <v>21.80396177360519</v>
       </c>
       <c r="D5" t="n">
-        <v>24.71321813660225</v>
+        <v>24.44616789486179</v>
       </c>
       <c r="E5" t="n">
-        <v>27.30303993888304</v>
+        <v>27.08837401611838</v>
       </c>
       <c r="F5" t="n">
-        <v>29.89286174116384</v>
+        <v>29.73058013737499</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.25772686724757</v>
+        <v>19.76209159125309</v>
       </c>
       <c r="C6" t="n">
-        <v>22.84754866952836</v>
+        <v>22.40429771250967</v>
       </c>
       <c r="D6" t="n">
-        <v>25.43737047180915</v>
+        <v>25.04650383376627</v>
       </c>
       <c r="E6" t="n">
-        <v>28.02719227408993</v>
+        <v>27.68870995502287</v>
       </c>
       <c r="F6" t="n">
-        <v>30.61701407637073</v>
+        <v>30.33091607627947</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>23.91</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>23.97</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>23.99</v>
+        <v>23.85</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.66</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30712.26878601086</v>
+        <v>29692.01398691984</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.203428111982207</v>
+        <v>1.16345049537675</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.5</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29692.01398691984</v>
+        <v>28480.4614129993</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.16345049537675</v>
+        <v>1.115977075657771</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.31</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28480.4614129993</v>
+        <v>36132.37240618177</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.115977075657771</v>
+        <v>1.415809200198693</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.8458319559573</v>
+        <v>23.97513840018773</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.58152919180447</v>
+        <v>22.90479530238055</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33100</v>
+        <v>35300</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31037.5</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.356938061630981</v>
+        <v>1.427365912532628</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36132.37240618177</v>
+        <v>36393.29990904735</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.415809200198693</v>
+        <v>1.371498123485484</v>
       </c>
     </row>
   </sheetData>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32500</v>
+        <v>35400</v>
       </c>
       <c r="C2" t="n">
-        <v>32700</v>
+        <v>35455</v>
       </c>
       <c r="D2" t="n">
-        <v>1.232626660216645</v>
+        <v>1.344067561910366</v>
       </c>
       <c r="E2" t="n">
-        <v>1.232626660216645</v>
+        <v>1.344067561910366</v>
       </c>
       <c r="F2" t="n">
-        <v>1.200883318472862</v>
+        <v>1.309454327164205</v>
       </c>
     </row>
     <row r="3">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33650</v>
+        <v>35200</v>
       </c>
       <c r="C3" t="n">
-        <v>33792.5</v>
+        <v>35265</v>
       </c>
       <c r="D3" t="n">
-        <v>1.244219775972388</v>
+        <v>1.314447981751099</v>
       </c>
       <c r="E3" t="n">
-        <v>1.244219775972388</v>
+        <v>1.314447981751099</v>
       </c>
       <c r="F3" t="n">
-        <v>1.180961148837576</v>
+        <v>1.24761881187979</v>
       </c>
     </row>
     <row r="4">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29500</v>
+        <v>30100</v>
       </c>
       <c r="C4" t="n">
-        <v>29850</v>
+        <v>30420</v>
       </c>
       <c r="D4" t="n">
-        <v>1.032981427531987</v>
+        <v>1.061433138453159</v>
       </c>
       <c r="E4" t="n">
-        <v>1.032981427531987</v>
+        <v>1.061433138453159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9552131204026875</v>
+        <v>0.9815228359943228</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28500</v>
+        <v>29100</v>
       </c>
       <c r="C5" t="n">
-        <v>28900</v>
+        <v>29470</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9821388443218247</v>
+        <v>1.010590555242997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9821388443218247</v>
+        <v>1.010590555242997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8848097696593015</v>
+        <v>0.9104419416603576</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27500</v>
+        <v>28100</v>
       </c>
       <c r="C6" t="n">
-        <v>27950</v>
+        <v>28520</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9312962611116623</v>
+        <v>0.9597479720328344</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9312962611116623</v>
+        <v>0.9597479720328344</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8173990636982428</v>
+        <v>0.8423711406180175</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26500</v>
+        <v>27100</v>
       </c>
       <c r="C7" t="n">
-        <v>27000</v>
+        <v>27570</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8804536779014998</v>
+        <v>0.9089053888226719</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8804536779014998</v>
+        <v>0.9089053888226719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7528735569999132</v>
+        <v>0.7772025380032188</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26000</v>
+        <v>26600</v>
       </c>
       <c r="C8" t="n">
-        <v>26525</v>
+        <v>27095</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8550323862964185</v>
+        <v>0.8834840972175906</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8550323862964185</v>
+        <v>0.8834840972175906</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7123072292597821</v>
+        <v>0.7360096757387328</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25500</v>
+        <v>26100</v>
       </c>
       <c r="C9" t="n">
-        <v>26050</v>
+        <v>26620</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8296110946913372</v>
+        <v>0.8580628056125094</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8296110946913372</v>
+        <v>0.8580628056125094</v>
       </c>
       <c r="F9" t="n">
-        <v>0.673330975319647</v>
+        <v>0.6964230221674452</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.177778182650012</v>
+        <v>7.50104429322609</v>
       </c>
     </row>
     <row r="11">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22.58152919180447</v>
+        <v>22.90479530238055</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31037.5</v>
+        <v>32450</v>
       </c>
     </row>
   </sheetData>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.36074783563515</v>
+        <v>17.45126234659645</v>
       </c>
       <c r="C2" t="n">
-        <v>20.00295395689174</v>
+        <v>20.09346846785304</v>
       </c>
       <c r="D2" t="n">
-        <v>22.64516007814833</v>
+        <v>22.73567458910964</v>
       </c>
       <c r="E2" t="n">
-        <v>25.28736619940493</v>
+        <v>25.37788071036623</v>
       </c>
       <c r="F2" t="n">
-        <v>27.92957232066153</v>
+        <v>28.02008683162283</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.96108377453963</v>
+        <v>18.0709942521355</v>
       </c>
       <c r="C3" t="n">
-        <v>20.60328989579622</v>
+        <v>20.71320037339209</v>
       </c>
       <c r="D3" t="n">
-        <v>23.24549601705282</v>
+        <v>23.35540649464868</v>
       </c>
       <c r="E3" t="n">
-        <v>25.88770213830941</v>
+        <v>25.99761261590528</v>
       </c>
       <c r="F3" t="n">
-        <v>28.52990825956602</v>
+        <v>28.63981873716189</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.56141971344412</v>
+        <v>18.69072615767455</v>
       </c>
       <c r="C4" t="n">
-        <v>21.20362583470071</v>
+        <v>21.33293227893114</v>
       </c>
       <c r="D4" t="n">
-        <v>23.8458319559573</v>
+        <v>23.97513840018773</v>
       </c>
       <c r="E4" t="n">
-        <v>26.4880380772139</v>
+        <v>26.61734452144433</v>
       </c>
       <c r="F4" t="n">
-        <v>29.1302441984705</v>
+        <v>29.25955064270094</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.1617556523486</v>
+        <v>19.31045806321359</v>
       </c>
       <c r="C5" t="n">
-        <v>21.80396177360519</v>
+        <v>21.95266418447019</v>
       </c>
       <c r="D5" t="n">
-        <v>24.44616789486179</v>
+        <v>24.59487030572678</v>
       </c>
       <c r="E5" t="n">
-        <v>27.08837401611838</v>
+        <v>27.23707642698338</v>
       </c>
       <c r="F5" t="n">
-        <v>29.73058013737499</v>
+        <v>29.87928254823998</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.76209159125309</v>
+        <v>19.93018996875265</v>
       </c>
       <c r="C6" t="n">
-        <v>22.40429771250967</v>
+        <v>22.57239609000924</v>
       </c>
       <c r="D6" t="n">
-        <v>25.04650383376627</v>
+        <v>25.21460221126583</v>
       </c>
       <c r="E6" t="n">
-        <v>27.68870995502287</v>
+        <v>27.85680833252243</v>
       </c>
       <c r="F6" t="n">
-        <v>30.33091607627947</v>
+        <v>30.49901445377903</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>23.78</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>23.83</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>23.85</v>
+        <v>23.98</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.51</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36393.29990904735</v>
+        <v>35365.67740838334</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.371498123485484</v>
+        <v>1.332771700357205</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.35</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35365.67740838334</v>
+        <v>36007.94147129834</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.332771700357205</v>
+        <v>1.356975714812379</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.45</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36007.94147129834</v>
+        <v>27465.82943452887</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.356975714812379</v>
+        <v>1.035062322558558</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.97513840018773</v>
+        <v>24.65388854231994</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.68870046539253</v>
+        <v>25.48349577387961</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.90479530238055</v>
+        <v>23.40947769498044</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.427365912532628</v>
+        <v>1.426351900659219</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27465.82943452887</v>
+        <v>23026.40487341708</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.035062322558558</v>
+        <v>0.8707775400423603</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>854.2028010894207</v>
+        <v>868.2913898322169</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>506.2775561706302</v>
+        <v>527.4867983176133</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1096.455357260051</v>
+        <v>1131.753188149829</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.68870046539253</v>
+        <v>25.48349577387961</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.68870046539253</v>
+        <v>25.48349577387961</v>
       </c>
     </row>
     <row r="14">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.48063872166389</v>
+        <v>20.11889464735242</v>
       </c>
       <c r="F11" t="n">
-        <v>15.40375100915445</v>
+        <v>15.90843340175435</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22.90479530238055</v>
+        <v>23.40947769498044</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.45126234659645</v>
+        <v>17.99426246030222</v>
       </c>
       <c r="C2" t="n">
-        <v>20.09346846785304</v>
+        <v>20.70434359577204</v>
       </c>
       <c r="D2" t="n">
-        <v>22.73567458910964</v>
+        <v>23.41442473124184</v>
       </c>
       <c r="E2" t="n">
-        <v>25.37788071036623</v>
+        <v>26.12450586671168</v>
       </c>
       <c r="F2" t="n">
-        <v>28.02008683162283</v>
+        <v>28.83458700218149</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.0709942521355</v>
+        <v>18.61399436584126</v>
       </c>
       <c r="C3" t="n">
-        <v>20.71320037339209</v>
+        <v>21.32407550131109</v>
       </c>
       <c r="D3" t="n">
-        <v>23.35540649464868</v>
+        <v>24.03415663678089</v>
       </c>
       <c r="E3" t="n">
-        <v>25.99761261590528</v>
+        <v>26.74423777225073</v>
       </c>
       <c r="F3" t="n">
-        <v>28.63981873716189</v>
+        <v>29.45431890772053</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.69072615767455</v>
+        <v>19.23372627138031</v>
       </c>
       <c r="C4" t="n">
-        <v>21.33293227893114</v>
+        <v>21.94380740685013</v>
       </c>
       <c r="D4" t="n">
-        <v>23.97513840018773</v>
+        <v>24.65388854231994</v>
       </c>
       <c r="E4" t="n">
-        <v>26.61734452144433</v>
+        <v>27.36396967778978</v>
       </c>
       <c r="F4" t="n">
-        <v>29.25955064270094</v>
+        <v>30.07405081325958</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.31045806321359</v>
+        <v>19.85345817691936</v>
       </c>
       <c r="C5" t="n">
-        <v>21.95266418447019</v>
+        <v>22.56353931238918</v>
       </c>
       <c r="D5" t="n">
-        <v>24.59487030572678</v>
+        <v>25.273620447859</v>
       </c>
       <c r="E5" t="n">
-        <v>27.23707642698338</v>
+        <v>27.98370158332883</v>
       </c>
       <c r="F5" t="n">
-        <v>29.87928254823998</v>
+        <v>30.69378271879863</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.93018996875265</v>
+        <v>20.47319008245842</v>
       </c>
       <c r="C6" t="n">
-        <v>22.57239609000924</v>
+        <v>23.18327121792823</v>
       </c>
       <c r="D6" t="n">
-        <v>25.21460221126583</v>
+        <v>25.89335235339804</v>
       </c>
       <c r="E6" t="n">
-        <v>27.85680833252243</v>
+        <v>28.60343348886788</v>
       </c>
       <c r="F6" t="n">
-        <v>30.49901445377903</v>
+        <v>31.31351462433768</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>23.9</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>23.96</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>23.98</v>
+        <v>24.65</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.12</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23026.40487341708</v>
+        <v>30322.84751562102</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8707775400423603</v>
+        <v>1.14670330483135</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.65388854231994</v>
+        <v>24.70564541030629</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.40947769498044</v>
+        <v>23.5388698649463</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32450</v>
+        <v>32743.75</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.426351900659219</v>
+        <v>1.438560239788666</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30322.84751562102</v>
+        <v>30248.26256486583</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.14670330483135</v>
+        <v>1.132516005246146</v>
       </c>
     </row>
   </sheetData>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35400</v>
+        <v>34900</v>
       </c>
       <c r="C2" t="n">
-        <v>35455</v>
+        <v>34980</v>
       </c>
       <c r="D2" t="n">
-        <v>1.344067561910366</v>
+        <v>1.333143957398875</v>
       </c>
       <c r="E2" t="n">
-        <v>1.344067561910366</v>
+        <v>1.333143957398875</v>
       </c>
       <c r="F2" t="n">
-        <v>1.309454327164205</v>
+        <v>1.298812033873925</v>
       </c>
     </row>
     <row r="3">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35200</v>
+        <v>35725</v>
       </c>
       <c r="C3" t="n">
-        <v>35265</v>
+        <v>35763.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.314447981751099</v>
+        <v>1.347422669010323</v>
       </c>
       <c r="E3" t="n">
-        <v>1.314447981751099</v>
+        <v>1.347422669010323</v>
       </c>
       <c r="F3" t="n">
-        <v>1.24761881187979</v>
+        <v>1.278916999949322</v>
       </c>
     </row>
     <row r="4">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30100</v>
+        <v>30675</v>
       </c>
       <c r="C4" t="n">
-        <v>30420</v>
+        <v>30966.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.061433138453159</v>
+        <v>1.082331453720188</v>
       </c>
       <c r="E4" t="n">
-        <v>1.061433138453159</v>
+        <v>1.082331453720188</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9815228359943228</v>
+        <v>1.00084781551992</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29100</v>
+        <v>29675</v>
       </c>
       <c r="C5" t="n">
-        <v>29470</v>
+        <v>30016.25</v>
       </c>
       <c r="D5" t="n">
-        <v>1.010590555242997</v>
+        <v>1.031488870510026</v>
       </c>
       <c r="E5" t="n">
-        <v>1.010590555242997</v>
+        <v>1.031488870510026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9104419416603576</v>
+        <v>0.9292692527117347</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28100</v>
+        <v>28675</v>
       </c>
       <c r="C6" t="n">
-        <v>28520</v>
+        <v>29066.25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9597479720328344</v>
+        <v>0.980646287299863</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9597479720328344</v>
+        <v>0.980646287299863</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8423711406180175</v>
+        <v>0.8607135994524913</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27100</v>
+        <v>27675</v>
       </c>
       <c r="C7" t="n">
-        <v>27570</v>
+        <v>28116.25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9089053888226719</v>
+        <v>0.9298037040897006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9089053888226719</v>
+        <v>0.9298037040897006</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7772025380032188</v>
+        <v>0.7950726308261529</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26600</v>
+        <v>27175</v>
       </c>
       <c r="C8" t="n">
-        <v>27095</v>
+        <v>27641.25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8834840972175906</v>
+        <v>0.9043824124846194</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8834840972175906</v>
+        <v>0.9043824124846194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7360096757387328</v>
+        <v>0.7534195672032347</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26100</v>
+        <v>26675</v>
       </c>
       <c r="C9" t="n">
-        <v>26620</v>
+        <v>27166.25</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8580628056125094</v>
+        <v>0.878961120879538</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8580628056125094</v>
+        <v>0.878961120879538</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6964230221674452</v>
+        <v>0.7133845636551723</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.50104429322609</v>
+        <v>7.630436463191952</v>
       </c>
     </row>
     <row r="11">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23.40947769498044</v>
+        <v>23.5388698649463</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32450</v>
+        <v>32743.75</v>
       </c>
     </row>
   </sheetData>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.99426246030222</v>
+        <v>18.03049226789266</v>
       </c>
       <c r="C2" t="n">
-        <v>20.70434359577204</v>
+        <v>20.74057340336248</v>
       </c>
       <c r="D2" t="n">
-        <v>23.41442473124184</v>
+        <v>23.45065453883229</v>
       </c>
       <c r="E2" t="n">
-        <v>26.12450586671168</v>
+        <v>26.16073567430212</v>
       </c>
       <c r="F2" t="n">
-        <v>28.83458700218149</v>
+        <v>28.87081680977192</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.61399436584126</v>
+        <v>18.65798770362966</v>
       </c>
       <c r="C3" t="n">
-        <v>21.32407550131109</v>
+        <v>21.36806883909948</v>
       </c>
       <c r="D3" t="n">
-        <v>24.03415663678089</v>
+        <v>24.07814997456929</v>
       </c>
       <c r="E3" t="n">
-        <v>26.74423777225073</v>
+        <v>26.78823111003913</v>
       </c>
       <c r="F3" t="n">
-        <v>29.45431890772053</v>
+        <v>29.49831224550893</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.23372627138031</v>
+        <v>19.28548313936666</v>
       </c>
       <c r="C4" t="n">
-        <v>21.94380740685013</v>
+        <v>21.99556427483648</v>
       </c>
       <c r="D4" t="n">
-        <v>24.65388854231994</v>
+        <v>24.70564541030629</v>
       </c>
       <c r="E4" t="n">
-        <v>27.36396967778978</v>
+        <v>27.41572654577612</v>
       </c>
       <c r="F4" t="n">
-        <v>30.07405081325958</v>
+        <v>30.12580768124593</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.85345817691936</v>
+        <v>19.91297857510366</v>
       </c>
       <c r="C5" t="n">
-        <v>22.56353931238918</v>
+        <v>22.62305971057348</v>
       </c>
       <c r="D5" t="n">
-        <v>25.273620447859</v>
+        <v>25.33314084604329</v>
       </c>
       <c r="E5" t="n">
-        <v>27.98370158332883</v>
+        <v>28.04322198151313</v>
       </c>
       <c r="F5" t="n">
-        <v>30.69378271879863</v>
+        <v>30.75330311698293</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.47319008245842</v>
+        <v>20.54047401084066</v>
       </c>
       <c r="C6" t="n">
-        <v>23.18327121792823</v>
+        <v>23.25055514631048</v>
       </c>
       <c r="D6" t="n">
-        <v>25.89335235339804</v>
+        <v>25.96063628178029</v>
       </c>
       <c r="E6" t="n">
-        <v>28.60343348886788</v>
+        <v>28.67071741725013</v>
       </c>
       <c r="F6" t="n">
-        <v>31.31351462433768</v>
+        <v>31.38079855271993</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.58</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>24.64</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>24.65</v>
+        <v>24.71</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.26</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30248.26256486583</v>
+        <v>39889.07693883435</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.132516005246146</v>
+        <v>1.493474806060326</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.70564541030629</v>
+        <v>25.13633652601548</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.48349577387961</v>
+        <v>25.98079548184381</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.5388698649463</v>
+        <v>23.86964809227297</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.438560239788666</v>
+        <v>1.437725935690331</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39889.07693883435</v>
+        <v>37009.71291262066</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.493474806060326</v>
+        <v>1.390520005631379</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>868.2913898322169</v>
+        <v>873.7580347523364</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>527.4867983176133</v>
+        <v>544.1058411284261</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1131.753188149829</v>
+        <v>1153.838875880762</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.48349577387961</v>
+        <v>25.98079548184381</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.48349577387961</v>
+        <v>25.98079548184381</v>
       </c>
     </row>
     <row r="14">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.11889464735242</v>
+        <v>20.53721945276597</v>
       </c>
       <c r="F11" t="n">
-        <v>15.90843340175435</v>
+        <v>16.23921162908102</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23.5388698649463</v>
+        <v>23.86964809227297</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.03049226789266</v>
+        <v>18.37504516046</v>
       </c>
       <c r="C2" t="n">
-        <v>20.74057340336248</v>
+        <v>21.12819540750073</v>
       </c>
       <c r="D2" t="n">
-        <v>23.45065453883229</v>
+        <v>23.88134565454147</v>
       </c>
       <c r="E2" t="n">
-        <v>26.16073567430212</v>
+        <v>26.63449590158221</v>
       </c>
       <c r="F2" t="n">
-        <v>28.87081680977192</v>
+        <v>29.38764614862294</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.65798770362966</v>
+        <v>19.002540596197</v>
       </c>
       <c r="C3" t="n">
-        <v>21.36806883909948</v>
+        <v>21.75569084323773</v>
       </c>
       <c r="D3" t="n">
-        <v>24.07814997456929</v>
+        <v>24.50884109027847</v>
       </c>
       <c r="E3" t="n">
-        <v>26.78823111003913</v>
+        <v>27.26199133731921</v>
       </c>
       <c r="F3" t="n">
-        <v>29.49831224550893</v>
+        <v>30.01514158435994</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.28548313936666</v>
+        <v>19.630036031934</v>
       </c>
       <c r="C4" t="n">
-        <v>21.99556427483648</v>
+        <v>22.38318627897473</v>
       </c>
       <c r="D4" t="n">
-        <v>24.70564541030629</v>
+        <v>25.13633652601548</v>
       </c>
       <c r="E4" t="n">
-        <v>27.41572654577612</v>
+        <v>27.88948677305621</v>
       </c>
       <c r="F4" t="n">
-        <v>30.12580768124593</v>
+        <v>30.64263702009694</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.91297857510366</v>
+        <v>20.25753146767101</v>
       </c>
       <c r="C5" t="n">
-        <v>22.62305971057348</v>
+        <v>23.01068171471173</v>
       </c>
       <c r="D5" t="n">
-        <v>25.33314084604329</v>
+        <v>25.76383196175248</v>
       </c>
       <c r="E5" t="n">
-        <v>28.04322198151313</v>
+        <v>28.51698220879321</v>
       </c>
       <c r="F5" t="n">
-        <v>30.75330311698293</v>
+        <v>31.27013245583394</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.54047401084066</v>
+        <v>20.88502690340801</v>
       </c>
       <c r="C6" t="n">
-        <v>23.25055514631048</v>
+        <v>23.63817715044873</v>
       </c>
       <c r="D6" t="n">
-        <v>25.96063628178029</v>
+        <v>26.39132739748948</v>
       </c>
       <c r="E6" t="n">
-        <v>28.67071741725013</v>
+        <v>29.14447764453021</v>
       </c>
       <c r="F6" t="n">
-        <v>31.38079855271993</v>
+        <v>31.89762789157094</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.63</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>24.69</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>24.71</v>
+        <v>25.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.77</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37009.71291262066</v>
+        <v>30583.71564756011</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.390520005631379</v>
+        <v>1.149083986543749</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.76</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30583.71564756011</v>
+        <v>27847.89502976203</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.149083986543749</v>
+        <v>1.046294394258914</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.13633652601548</v>
+        <v>24.51191933629867</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.98079548184381</v>
+        <v>25.25515242124413</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.86964809227297</v>
+        <v>23.39706970888048</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.437725935690331</v>
+        <v>1.440768983169153</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27847.89502976203</v>
+        <v>32091.04358426798</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.046294394258914</v>
+        <v>1.190630962013667</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>873.7580347523364</v>
+        <v>910.445703953288</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>544.1058411284261</v>
+        <v>517.9998755614866</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.77</v>
+        <v>73.587</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.821</v>
+        <v>16.848</v>
       </c>
     </row>
     <row r="6">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5.616</v>
+        <v>-5.693</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="9">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1153.838875880762</v>
+        <v>1125.687579514774</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44411222</v>
+        <v>44572591</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.98079548184381</v>
+        <v>25.25515242124413</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.98079548184381</v>
+        <v>25.25515242124413</v>
       </c>
     </row>
     <row r="14">
@@ -822,13 +822,13 @@
         <v>34980</v>
       </c>
       <c r="D2" t="n">
-        <v>1.333143957398875</v>
+        <v>1.357880281179975</v>
       </c>
       <c r="E2" t="n">
-        <v>1.333143957398875</v>
+        <v>1.357880281179975</v>
       </c>
       <c r="F2" t="n">
-        <v>1.298812033873925</v>
+        <v>1.322911332994913</v>
       </c>
     </row>
     <row r="3">
@@ -844,13 +844,13 @@
         <v>35763.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.347422669010323</v>
+        <v>1.374305677563146</v>
       </c>
       <c r="E3" t="n">
-        <v>1.347422669010323</v>
+        <v>1.374305677563146</v>
       </c>
       <c r="F3" t="n">
-        <v>1.278916999949322</v>
+        <v>1.304433222467116</v>
       </c>
     </row>
     <row r="4">
@@ -866,13 +866,13 @@
         <v>30966.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.082331453720188</v>
+        <v>1.103799241219789</v>
       </c>
       <c r="E4" t="n">
-        <v>1.082331453720188</v>
+        <v>1.103799241219789</v>
       </c>
       <c r="F4" t="n">
-        <v>1.00084781551992</v>
+        <v>1.020699394395476</v>
       </c>
     </row>
     <row r="5">
@@ -888,13 +888,13 @@
         <v>30016.25</v>
       </c>
       <c r="D5" t="n">
-        <v>1.031488870510026</v>
+        <v>1.051812570756768</v>
       </c>
       <c r="E5" t="n">
-        <v>1.031488870510026</v>
+        <v>1.051812570756768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9292692527117347</v>
+        <v>0.9475788925736652</v>
       </c>
     </row>
     <row r="6">
@@ -910,13 +910,13 @@
         <v>29066.25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.980646287299863</v>
+        <v>0.9998259002937477</v>
       </c>
       <c r="E6" t="n">
-        <v>0.980646287299863</v>
+        <v>0.9998259002937477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8607135994524913</v>
+        <v>0.8775475526829942</v>
       </c>
     </row>
     <row r="7">
@@ -932,13 +932,13 @@
         <v>28116.25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9298037040897006</v>
+        <v>0.9478392298307272</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9298037040897006</v>
+        <v>0.9478392298307272</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7950726308261529</v>
+        <v>0.8104947600736262</v>
       </c>
     </row>
     <row r="8">
@@ -954,13 +954,13 @@
         <v>27641.25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9043824124846194</v>
+        <v>0.921845894599217</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9043824124846194</v>
+        <v>0.921845894599217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7534195672032347</v>
+        <v>0.7679679805237616</v>
       </c>
     </row>
     <row r="9">
@@ -976,13 +976,13 @@
         <v>27166.25</v>
       </c>
       <c r="D9" t="n">
-        <v>0.878961120879538</v>
+        <v>0.8958525593677064</v>
       </c>
       <c r="E9" t="n">
-        <v>0.878961120879538</v>
+        <v>0.8958525593677064</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7133845636551723</v>
+        <v>0.7270940340619318</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.630436463191952</v>
+        <v>7.778727169773485</v>
       </c>
     </row>
     <row r="11">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.53721945276597</v>
+        <v>19.75202587049862</v>
       </c>
       <c r="F11" t="n">
-        <v>16.23921162908102</v>
+        <v>15.61834253910699</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23.86964809227297</v>
+        <v>23.39706970888048</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.37504516046</v>
+        <v>17.69963032919588</v>
       </c>
       <c r="C2" t="n">
-        <v>21.12819540750073</v>
+        <v>20.46205936145672</v>
       </c>
       <c r="D2" t="n">
-        <v>23.88134565454147</v>
+        <v>23.22448839371756</v>
       </c>
       <c r="E2" t="n">
-        <v>26.63449590158221</v>
+        <v>25.98691742597841</v>
       </c>
       <c r="F2" t="n">
-        <v>29.38764614862294</v>
+        <v>28.74934645823924</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.002540596197</v>
+        <v>18.34334580048643</v>
       </c>
       <c r="C3" t="n">
-        <v>21.75569084323773</v>
+        <v>21.10577483274727</v>
       </c>
       <c r="D3" t="n">
-        <v>24.50884109027847</v>
+        <v>23.86820386500811</v>
       </c>
       <c r="E3" t="n">
-        <v>27.26199133731921</v>
+        <v>26.63063289726897</v>
       </c>
       <c r="F3" t="n">
-        <v>30.01514158435994</v>
+        <v>29.3930619295298</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.630036031934</v>
+        <v>18.98706127177699</v>
       </c>
       <c r="C4" t="n">
-        <v>22.38318627897473</v>
+        <v>21.74949030403783</v>
       </c>
       <c r="D4" t="n">
-        <v>25.13633652601548</v>
+        <v>24.51191933629867</v>
       </c>
       <c r="E4" t="n">
-        <v>27.88948677305621</v>
+        <v>27.27434836855952</v>
       </c>
       <c r="F4" t="n">
-        <v>30.64263702009694</v>
+        <v>30.03677740082036</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.25753146767101</v>
+        <v>19.63077674306754</v>
       </c>
       <c r="C5" t="n">
-        <v>23.01068171471173</v>
+        <v>22.39320577532838</v>
       </c>
       <c r="D5" t="n">
-        <v>25.76383196175248</v>
+        <v>25.15563480758922</v>
       </c>
       <c r="E5" t="n">
-        <v>28.51698220879321</v>
+        <v>27.91806383985008</v>
       </c>
       <c r="F5" t="n">
-        <v>31.27013245583394</v>
+        <v>30.68049287211091</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.88502690340801</v>
+        <v>20.2744922143581</v>
       </c>
       <c r="C6" t="n">
-        <v>23.63817715044873</v>
+        <v>23.03692124661894</v>
       </c>
       <c r="D6" t="n">
-        <v>26.39132739748948</v>
+        <v>25.79935027887978</v>
       </c>
       <c r="E6" t="n">
-        <v>29.14447764453021</v>
+        <v>28.56177931114063</v>
       </c>
       <c r="F6" t="n">
-        <v>31.89762789157094</v>
+        <v>31.32420834340147</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.06</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.12</v>
+        <v>24.49</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.14</v>
+        <v>24.51</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.51191933629867</v>
+        <v>24.61932701136015</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.25515242124413</v>
+        <v>25.37562015981036</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.39706970888048</v>
+        <v>23.48488728868485</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.440768983169153</v>
+        <v>1.440892912110643</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32091.04358426798</v>
+        <v>31432.59567760261</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.190630962013667</v>
+        <v>1.165602588488757</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>910.445703953288</v>
+        <v>915.1114771495851</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>517.9998755614866</v>
+        <v>518.703661604997</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1125.687579514774</v>
+        <v>1131.057138754582</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.25515242124413</v>
+        <v>25.37562015981036</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.25515242124413</v>
+        <v>25.37562015981036</v>
       </c>
     </row>
     <row r="14">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.75202587049862</v>
+        <v>19.86308599764318</v>
       </c>
       <c r="F11" t="n">
-        <v>15.61834253910699</v>
+        <v>15.70616011891136</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23.39706970888048</v>
+        <v>23.48488728868485</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.69963032919588</v>
+        <v>17.78555646924506</v>
       </c>
       <c r="C2" t="n">
-        <v>20.46205936145672</v>
+        <v>20.55872626901206</v>
       </c>
       <c r="D2" t="n">
-        <v>23.22448839371756</v>
+        <v>23.33189606877904</v>
       </c>
       <c r="E2" t="n">
-        <v>25.98691742597841</v>
+        <v>26.10506586854604</v>
       </c>
       <c r="F2" t="n">
-        <v>28.74934645823924</v>
+        <v>28.87823566831302</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.34334580048643</v>
+        <v>18.42927194053562</v>
       </c>
       <c r="C3" t="n">
-        <v>21.10577483274727</v>
+        <v>21.20244174030262</v>
       </c>
       <c r="D3" t="n">
-        <v>23.86820386500811</v>
+        <v>23.9756115400696</v>
       </c>
       <c r="E3" t="n">
-        <v>26.63063289726897</v>
+        <v>26.7487813398366</v>
       </c>
       <c r="F3" t="n">
-        <v>29.3930619295298</v>
+        <v>29.52195113960357</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.98706127177699</v>
+        <v>19.07298741182617</v>
       </c>
       <c r="C4" t="n">
-        <v>21.74949030403783</v>
+        <v>21.84615721159317</v>
       </c>
       <c r="D4" t="n">
-        <v>24.51191933629867</v>
+        <v>24.61932701136015</v>
       </c>
       <c r="E4" t="n">
-        <v>27.27434836855952</v>
+        <v>27.39249681112716</v>
       </c>
       <c r="F4" t="n">
-        <v>30.03677740082036</v>
+        <v>30.16566661089413</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.63077674306754</v>
+        <v>19.71670288311672</v>
       </c>
       <c r="C5" t="n">
-        <v>22.39320577532838</v>
+        <v>22.48987268288373</v>
       </c>
       <c r="D5" t="n">
-        <v>25.15563480758922</v>
+        <v>25.26304248265071</v>
       </c>
       <c r="E5" t="n">
-        <v>27.91806383985008</v>
+        <v>28.03621228241771</v>
       </c>
       <c r="F5" t="n">
-        <v>30.68049287211091</v>
+        <v>30.80938208218468</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2744922143581</v>
+        <v>20.36041835440728</v>
       </c>
       <c r="C6" t="n">
-        <v>23.03692124661894</v>
+        <v>23.13358815417429</v>
       </c>
       <c r="D6" t="n">
-        <v>25.79935027887978</v>
+        <v>25.90675795394127</v>
       </c>
       <c r="E6" t="n">
-        <v>28.56177931114063</v>
+        <v>28.67992775370827</v>
       </c>
       <c r="F6" t="n">
-        <v>31.32420834340147</v>
+        <v>31.45309755347524</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.44</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>24.49</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>24.51</v>
+        <v>24.62</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.61932701136015</v>
+        <v>24.83078475079182</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.48488728868485</v>
+        <v>24.01353163726402</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35300</v>
+        <v>31550</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32743.75</v>
+        <v>33287.5</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.440892912110643</v>
+        <v>1.28645208583593</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31432.59567760261</v>
+        <v>30423.20159250708</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.165602588488757</v>
+        <v>1.110865417974561</v>
       </c>
     </row>
   </sheetData>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34900</v>
+        <v>38800</v>
       </c>
       <c r="C2" t="n">
-        <v>34980</v>
+        <v>38685</v>
       </c>
       <c r="D2" t="n">
-        <v>1.357880281179975</v>
+        <v>1.508856698503347</v>
       </c>
       <c r="E2" t="n">
-        <v>1.357880281179975</v>
+        <v>1.508856698503347</v>
       </c>
       <c r="F2" t="n">
-        <v>1.322911332994913</v>
+        <v>1.469999714982829</v>
       </c>
     </row>
     <row r="3">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35725</v>
+        <v>37250</v>
       </c>
       <c r="C3" t="n">
-        <v>35763.75</v>
+        <v>37212.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.374305677563146</v>
+        <v>1.448801099716191</v>
       </c>
       <c r="E3" t="n">
-        <v>1.374305677563146</v>
+        <v>1.448801099716191</v>
       </c>
       <c r="F3" t="n">
-        <v>1.304433222467116</v>
+        <v>1.375141148050637</v>
       </c>
     </row>
     <row r="4">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30675</v>
+        <v>25875</v>
       </c>
       <c r="C4" t="n">
-        <v>30966.25</v>
+        <v>26406.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.103799241219789</v>
+        <v>0.9208267054746716</v>
       </c>
       <c r="E4" t="n">
-        <v>1.103799241219789</v>
+        <v>0.9208267054746716</v>
       </c>
       <c r="F4" t="n">
-        <v>1.020699394395476</v>
+        <v>0.8515019992064187</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29675</v>
+        <v>31225</v>
       </c>
       <c r="C5" t="n">
-        <v>30016.25</v>
+        <v>31488.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.051812570756768</v>
+        <v>1.110897452091129</v>
       </c>
       <c r="E5" t="n">
-        <v>1.051812570756768</v>
+        <v>1.110897452091129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9475788925736652</v>
+        <v>1.000808515397414</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28675</v>
+        <v>31250</v>
       </c>
       <c r="C6" t="n">
-        <v>29066.25</v>
+        <v>31512.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9998259002937477</v>
+        <v>1.097983041865347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9998259002937477</v>
+        <v>1.097983041865347</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8775475526829942</v>
+        <v>0.9637001111826371</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27675</v>
+        <v>31250</v>
       </c>
       <c r="C7" t="n">
-        <v>28116.25</v>
+        <v>31512.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9478392298307272</v>
+        <v>1.084115649682559</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9478392298307272</v>
+        <v>1.084115649682559</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8104947600736262</v>
+        <v>0.9270243578528075</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27175</v>
+        <v>30750</v>
       </c>
       <c r="C8" t="n">
-        <v>27641.25</v>
+        <v>31037.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.921845894599217</v>
+        <v>1.058122314451049</v>
       </c>
       <c r="E8" t="n">
-        <v>0.921845894599217</v>
+        <v>1.058122314451049</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7679679805237616</v>
+        <v>0.8814966381440467</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26675</v>
+        <v>30250</v>
       </c>
       <c r="C9" t="n">
-        <v>27166.25</v>
+        <v>30562.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8958525593677064</v>
+        <v>1.032128979219539</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8958525593677064</v>
+        <v>1.032128979219539</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7270940340619318</v>
+        <v>0.8376990335358644</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.778727169773485</v>
+        <v>8.307371518352653</v>
       </c>
     </row>
     <row r="11">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23.48488728868485</v>
+        <v>24.01353163726402</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32743.75</v>
+        <v>33287.5</v>
       </c>
     </row>
   </sheetData>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.78555646924506</v>
+        <v>17.93357688684723</v>
       </c>
       <c r="C2" t="n">
-        <v>20.55872626901206</v>
+        <v>20.70674668661423</v>
       </c>
       <c r="D2" t="n">
-        <v>23.33189606877904</v>
+        <v>23.47991648638121</v>
       </c>
       <c r="E2" t="n">
-        <v>26.10506586854604</v>
+        <v>26.25308628614821</v>
       </c>
       <c r="F2" t="n">
-        <v>28.87823566831302</v>
+        <v>29.02625608591519</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.42927194053562</v>
+        <v>18.60901101905253</v>
       </c>
       <c r="C3" t="n">
-        <v>21.20244174030262</v>
+        <v>21.38218081881953</v>
       </c>
       <c r="D3" t="n">
-        <v>23.9756115400696</v>
+        <v>24.15535061858651</v>
       </c>
       <c r="E3" t="n">
-        <v>26.7487813398366</v>
+        <v>26.92852041835352</v>
       </c>
       <c r="F3" t="n">
-        <v>29.52195113960357</v>
+        <v>29.70169021812049</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.07298741182617</v>
+        <v>19.28444515125784</v>
       </c>
       <c r="C4" t="n">
-        <v>21.84615721159317</v>
+        <v>22.05761495102484</v>
       </c>
       <c r="D4" t="n">
-        <v>24.61932701136015</v>
+        <v>24.83078475079182</v>
       </c>
       <c r="E4" t="n">
-        <v>27.39249681112716</v>
+        <v>27.60395455055883</v>
       </c>
       <c r="F4" t="n">
-        <v>30.16566661089413</v>
+        <v>30.3771243503258</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.71670288311672</v>
+        <v>19.95987928346315</v>
       </c>
       <c r="C5" t="n">
-        <v>22.48987268288373</v>
+        <v>22.73304908323015</v>
       </c>
       <c r="D5" t="n">
-        <v>25.26304248265071</v>
+        <v>25.50621888299712</v>
       </c>
       <c r="E5" t="n">
-        <v>28.03621228241771</v>
+        <v>28.27938868276413</v>
       </c>
       <c r="F5" t="n">
-        <v>30.80938208218468</v>
+        <v>31.0525584825311</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.36041835440728</v>
+        <v>20.63531341566845</v>
       </c>
       <c r="C6" t="n">
-        <v>23.13358815417429</v>
+        <v>23.40848321543545</v>
       </c>
       <c r="D6" t="n">
-        <v>25.90675795394127</v>
+        <v>26.18165301520244</v>
       </c>
       <c r="E6" t="n">
-        <v>28.67992775370827</v>
+        <v>28.95482281496944</v>
       </c>
       <c r="F6" t="n">
-        <v>31.45309755347524</v>
+        <v>31.72799261473641</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.54</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>24.6</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>24.62</v>
+        <v>24.83</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.83078475079182</v>
+        <v>24.61305398509885</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.37562015981036</v>
+        <v>25.11828961744494</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.01353163726402</v>
+        <v>23.85520053657972</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.28645208583593</v>
+        <v>1.287129253540819</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30423.20159250708</v>
+        <v>31844.7686018742</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.110865417974561</v>
+        <v>1.159218933582828</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>518.703661604997</v>
+        <v>507.233772588335</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1131.057138754582</v>
+        <v>1119.58724973792</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.37562015981036</v>
+        <v>25.11828961744494</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.37562015981036</v>
+        <v>25.11828961744494</v>
       </c>
     </row>
     <row r="14">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.86308599764318</v>
+        <v>19.66284964164124</v>
       </c>
       <c r="F11" t="n">
-        <v>15.70616011891136</v>
+        <v>15.54782901822706</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.01353163726402</v>
+        <v>23.85520053657972</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.93357688684723</v>
+        <v>17.75939227429285</v>
       </c>
       <c r="C2" t="n">
-        <v>20.70674668661423</v>
+        <v>20.51078899749054</v>
       </c>
       <c r="D2" t="n">
-        <v>23.47991648638121</v>
+        <v>23.26218572068824</v>
       </c>
       <c r="E2" t="n">
-        <v>26.25308628614821</v>
+        <v>26.01358244388593</v>
       </c>
       <c r="F2" t="n">
-        <v>29.02625608591519</v>
+        <v>28.76497916708362</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.60901101905253</v>
+        <v>18.43482640649815</v>
       </c>
       <c r="C3" t="n">
-        <v>21.38218081881953</v>
+        <v>21.18622312969585</v>
       </c>
       <c r="D3" t="n">
-        <v>24.15535061858651</v>
+        <v>23.93761985289354</v>
       </c>
       <c r="E3" t="n">
-        <v>26.92852041835352</v>
+        <v>26.68901657609123</v>
       </c>
       <c r="F3" t="n">
-        <v>29.70169021812049</v>
+        <v>29.44041329928893</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.28444515125784</v>
+        <v>19.11026053870346</v>
       </c>
       <c r="C4" t="n">
-        <v>22.05761495102484</v>
+        <v>21.86165726190116</v>
       </c>
       <c r="D4" t="n">
-        <v>24.83078475079182</v>
+        <v>24.61305398509885</v>
       </c>
       <c r="E4" t="n">
-        <v>27.60395455055883</v>
+        <v>27.36445070829654</v>
       </c>
       <c r="F4" t="n">
-        <v>30.3771243503258</v>
+        <v>30.11584743149423</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.95987928346315</v>
+        <v>19.78569467090876</v>
       </c>
       <c r="C5" t="n">
-        <v>22.73304908323015</v>
+        <v>22.53709139410646</v>
       </c>
       <c r="D5" t="n">
-        <v>25.50621888299712</v>
+        <v>25.28848811730415</v>
       </c>
       <c r="E5" t="n">
-        <v>28.27938868276413</v>
+        <v>28.03988484050184</v>
       </c>
       <c r="F5" t="n">
-        <v>31.0525584825311</v>
+        <v>30.79128156369954</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.63531341566845</v>
+        <v>20.46112880311407</v>
       </c>
       <c r="C6" t="n">
-        <v>23.40848321543545</v>
+        <v>23.21252552631177</v>
       </c>
       <c r="D6" t="n">
-        <v>26.18165301520244</v>
+        <v>25.96392224950946</v>
       </c>
       <c r="E6" t="n">
-        <v>28.95482281496944</v>
+        <v>28.71531897270715</v>
       </c>
       <c r="F6" t="n">
-        <v>31.72799261473641</v>
+        <v>31.46671569590485</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.75</v>
+        <v>24.53</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>24.81</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>24.83</v>
+        <v>24.61</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.33</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31844.7686018742</v>
+        <v>31417.71840415186</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.159218933582828</v>
+        <v>1.143673376289601</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.8</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.26</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31417.71840415186</v>
+        <v>38006.49288329689</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.143673376289601</v>
+        <v>1.383519117385133</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.34</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38006.49288329689</v>
+        <v>43985.19565141</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.383519117385133</v>
+        <v>1.601156919490339</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.32</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43985.19565141</v>
+        <v>35200.16301254994</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.601156919490339</v>
+        <v>1.281362598029629</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.61305398509885</v>
+        <v>25.01739597917714</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.85520053657972</v>
+        <v>24.86605552177545</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31550</v>
+        <v>35425</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33287.5</v>
+        <v>36447</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.287129253540819</v>
+        <v>1.417214685141987</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35200.16301254994</v>
+        <v>34988.72099543057</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.281362598029629</v>
+        <v>1.175782045967022</v>
       </c>
     </row>
   </sheetData>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38800</v>
+        <v>41313</v>
       </c>
       <c r="C2" t="n">
-        <v>38685</v>
+        <v>41072.35</v>
       </c>
       <c r="D2" t="n">
-        <v>1.508856698503347</v>
+        <v>1.610428524897733</v>
       </c>
       <c r="E2" t="n">
-        <v>1.508856698503347</v>
+        <v>1.610428524897733</v>
       </c>
       <c r="F2" t="n">
-        <v>1.469999714982829</v>
+        <v>1.568955802726706</v>
       </c>
     </row>
     <row r="3">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37250</v>
+        <v>42125</v>
       </c>
       <c r="C3" t="n">
-        <v>37212.5</v>
+        <v>41843.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.448801099716191</v>
+        <v>1.660449043112616</v>
       </c>
       <c r="E3" t="n">
-        <v>1.448801099716191</v>
+        <v>1.660449043112616</v>
       </c>
       <c r="F3" t="n">
-        <v>1.375141148050637</v>
+        <v>1.576028485809925</v>
       </c>
     </row>
     <row r="4">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25875</v>
+        <v>28725</v>
       </c>
       <c r="C4" t="n">
-        <v>26406.25</v>
+        <v>29113.75</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9208267054746716</v>
+        <v>1.031200072596184</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9208267054746716</v>
+        <v>1.031200072596184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8515019992064187</v>
+        <v>0.9535658752911861</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31225</v>
+        <v>33625</v>
       </c>
       <c r="C5" t="n">
-        <v>31488.75</v>
+        <v>33768.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.110897452091129</v>
+        <v>1.234948979272935</v>
       </c>
       <c r="E5" t="n">
-        <v>1.110897452091129</v>
+        <v>1.234948979272935</v>
       </c>
       <c r="F5" t="n">
-        <v>1.000808515397414</v>
+        <v>1.112566647993635</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="C6" t="n">
-        <v>31512.5</v>
+        <v>33768.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.097983041865347</v>
+        <v>1.23492586695263</v>
       </c>
       <c r="E6" t="n">
-        <v>1.097983041865347</v>
+        <v>1.23492586695263</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9637001111826371</v>
+        <v>1.083894878069086</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="C7" t="n">
-        <v>31512.5</v>
+        <v>33768.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.084115649682559</v>
+        <v>1.23492586695263</v>
       </c>
       <c r="E7" t="n">
-        <v>1.084115649682559</v>
+        <v>1.23492586695263</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9270243578528075</v>
+        <v>1.055981766468176</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30750</v>
+        <v>33125</v>
       </c>
       <c r="C8" t="n">
-        <v>31037.5</v>
+        <v>33293.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.058122314451049</v>
+        <v>1.20893253172112</v>
       </c>
       <c r="E8" t="n">
-        <v>1.058122314451049</v>
+        <v>1.20893253172112</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8814966381440467</v>
+        <v>1.007133058155006</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30250</v>
+        <v>32625</v>
       </c>
       <c r="C9" t="n">
-        <v>30562.5</v>
+        <v>32818.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.032128979219539</v>
+        <v>1.18293919648961</v>
       </c>
       <c r="E9" t="n">
-        <v>1.032128979219539</v>
+        <v>1.18293919648961</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8376990335358644</v>
+        <v>0.960099989034664</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.307371518352653</v>
+        <v>9.318226503548384</v>
       </c>
     </row>
     <row r="11">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23.85520053657972</v>
+        <v>24.86605552177545</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33287.5</v>
+        <v>36447</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1045,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.75939227429285</v>
+        <v>18.04243167014765</v>
       </c>
       <c r="C2" t="n">
-        <v>20.51078899749054</v>
+        <v>20.79382839334535</v>
       </c>
       <c r="D2" t="n">
-        <v>23.26218572068824</v>
+        <v>23.54522511654304</v>
       </c>
       <c r="E2" t="n">
-        <v>26.01358244388593</v>
+        <v>26.29662183974073</v>
       </c>
       <c r="F2" t="n">
-        <v>28.76497916708362</v>
+        <v>29.04801856293842</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.43482640649815</v>
+        <v>18.7785171014647</v>
       </c>
       <c r="C3" t="n">
-        <v>21.18622312969585</v>
+        <v>21.5299138246624</v>
       </c>
       <c r="D3" t="n">
-        <v>23.93761985289354</v>
+        <v>24.28131054786009</v>
       </c>
       <c r="E3" t="n">
-        <v>26.68901657609123</v>
+        <v>27.03270727105778</v>
       </c>
       <c r="F3" t="n">
-        <v>29.44041329928893</v>
+        <v>29.78410399425547</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.11026053870346</v>
+        <v>19.51460253278175</v>
       </c>
       <c r="C4" t="n">
-        <v>21.86165726190116</v>
+        <v>22.26599925597945</v>
       </c>
       <c r="D4" t="n">
-        <v>24.61305398509885</v>
+        <v>25.01739597917714</v>
       </c>
       <c r="E4" t="n">
-        <v>27.36445070829654</v>
+        <v>27.76879270237483</v>
       </c>
       <c r="F4" t="n">
-        <v>30.11584743149423</v>
+        <v>30.52018942557253</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.78569467090876</v>
+        <v>20.2506879640988</v>
       </c>
       <c r="C5" t="n">
-        <v>22.53709139410646</v>
+        <v>23.0020846872965</v>
       </c>
       <c r="D5" t="n">
-        <v>25.28848811730415</v>
+        <v>25.75348141049419</v>
       </c>
       <c r="E5" t="n">
-        <v>28.03988484050184</v>
+        <v>28.50487813369188</v>
       </c>
       <c r="F5" t="n">
-        <v>30.79128156369954</v>
+        <v>31.25627485688958</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.46112880311407</v>
+        <v>20.98677339541585</v>
       </c>
       <c r="C6" t="n">
-        <v>23.21252552631177</v>
+        <v>23.73817011861355</v>
       </c>
       <c r="D6" t="n">
-        <v>25.96392224950946</v>
+        <v>26.48956684181124</v>
       </c>
       <c r="E6" t="n">
-        <v>28.71531897270715</v>
+        <v>29.24096356500893</v>
       </c>
       <c r="F6" t="n">
-        <v>31.46671569590485</v>
+        <v>31.99236028820663</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.53</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>24.59</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>24.61</v>
+        <v>25.02</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gnk_fv_report.xlsx
+++ b/outputs/gnk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.01739597917714</v>
+        <v>25.42170985137687</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.11828961744494</v>
+        <v>25.37338888411253</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.86605552177545</v>
+        <v>25.49419130227337</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35425</v>
+        <v>37300</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36447</v>
+        <v>38552.25</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.417214685141987</v>
+        <v>1.486246899426601</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34988.72099543057</v>
+        <v>34013.01730408923</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.175782045967022</v>
+        <v>1.089942427718757</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>507.233772588335</v>
+        <v>518.6042078659095</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1119.58724973792</v>
+        <v>1130.957685015494</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.11828961744494</v>
+        <v>25.37338888411253</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.11828961744494</v>
+        <v>25.37338888411253</v>
       </c>
     </row>
     <row r="14">
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41313</v>
+        <v>45250</v>
       </c>
       <c r="C2" t="n">
-        <v>41072.35</v>
+        <v>44812.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.610428524897733</v>
+        <v>1.770326859616485</v>
       </c>
       <c r="E2" t="n">
-        <v>1.610428524897733</v>
+        <v>1.770326859616485</v>
       </c>
       <c r="F2" t="n">
-        <v>1.568955802726706</v>
+        <v>1.724736339537089</v>
       </c>
     </row>
     <row r="3">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42125</v>
+        <v>44475</v>
       </c>
       <c r="C3" t="n">
-        <v>41843.75</v>
+        <v>44076.25</v>
       </c>
       <c r="D3" t="n">
-        <v>1.660449043112616</v>
+        <v>1.765237253831621</v>
       </c>
       <c r="E3" t="n">
-        <v>1.660449043112616</v>
+        <v>1.765237253831621</v>
       </c>
       <c r="F3" t="n">
-        <v>1.576028485809925</v>
+        <v>1.675489053874466</v>
       </c>
     </row>
     <row r="4">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28725</v>
+        <v>30125</v>
       </c>
       <c r="C4" t="n">
-        <v>29113.75</v>
+        <v>30443.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.031200072596184</v>
+        <v>1.104212534447459</v>
       </c>
       <c r="E4" t="n">
-        <v>1.031200072596184</v>
+        <v>1.104212534447459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9535658752911861</v>
+        <v>1.021081572722328</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33625</v>
+        <v>34359</v>
       </c>
       <c r="C5" t="n">
-        <v>33768.75</v>
+        <v>34466.05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.234948979272935</v>
+        <v>1.269469316176841</v>
       </c>
       <c r="E5" t="n">
-        <v>1.234948979272935</v>
+        <v>1.269469316176841</v>
       </c>
       <c r="F5" t="n">
-        <v>1.112566647993635</v>
+        <v>1.143666050609766</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="C6" t="n">
-        <v>33768.75</v>
+        <v>34465.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.23492586695263</v>
+        <v>1.26943119689856</v>
       </c>
       <c r="E6" t="n">
-        <v>1.23492586695263</v>
+        <v>1.26943119689856</v>
       </c>
       <c r="F6" t="n">
-        <v>1.083894878069086</v>
+        <v>1.114180218586544</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="C7" t="n">
-        <v>33768.75</v>
+        <v>34465.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.23492586695263</v>
+        <v>1.269408084578256</v>
       </c>
       <c r="E7" t="n">
-        <v>1.23492586695263</v>
+        <v>1.269408084578256</v>
       </c>
       <c r="F7" t="n">
-        <v>1.055981766468176</v>
+        <v>1.085467417432717</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33125</v>
+        <v>33858</v>
       </c>
       <c r="C8" t="n">
-        <v>33293.75</v>
+        <v>33990.1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.20893253172112</v>
+        <v>1.243414749346746</v>
       </c>
       <c r="E8" t="n">
-        <v>1.20893253172112</v>
+        <v>1.243414749346746</v>
       </c>
       <c r="F8" t="n">
-        <v>1.007133058155006</v>
+        <v>1.035859376934617</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32625</v>
+        <v>33358</v>
       </c>
       <c r="C9" t="n">
-        <v>32818.75</v>
+        <v>33515.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.18293919648961</v>
+        <v>1.217421414115235</v>
       </c>
       <c r="E9" t="n">
-        <v>1.18293919648961</v>
+        <v>1.217421414115235</v>
       </c>
       <c r="F9" t="n">
-        <v>0.960099989034664</v>
+        <v>0.9880865304076251</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.318226503548384</v>
+        <v>9.788566560105153</v>
       </c>
     </row>
     <row r="11">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.66284964164124</v>
+        <v>19.86240892353916</v>
       </c>
       <c r="F11" t="n">
-        <v>15.54782901822706</v>
+        <v>15.70562474216822</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.86605552177545</v>
+        <v>25.49419130227337</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36447</v>
+        <v>38552.25</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1045,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.04243167014765</v>
+        <v>18.34706916564517</v>
       </c>
       <c r="C2" t="n">
-        <v>20.79382839334535</v>
+        <v>21.12008367380056</v>
       </c>
       <c r="D2" t="n">
-        <v>23.54522511654304</v>
+        <v>23.89309818195596</v>
       </c>
       <c r="E2" t="n">
-        <v>26.29662183974073</v>
+        <v>26.66611269011137</v>
       </c>
       <c r="F2" t="n">
-        <v>29.04801856293842</v>
+        <v>29.43912719826676</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.7785171014647</v>
+        <v>19.11137500035563</v>
       </c>
       <c r="C3" t="n">
-        <v>21.5299138246624</v>
+        <v>21.88438950851101</v>
       </c>
       <c r="D3" t="n">
-        <v>24.28131054786009</v>
+        <v>24.65740401666641</v>
       </c>
       <c r="E3" t="n">
-        <v>27.03270727105778</v>
+        <v>27.43041852482182</v>
       </c>
       <c r="F3" t="n">
-        <v>29.78410399425547</v>
+        <v>30.20343303297721</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.51460253278175</v>
+        <v>19.87568083506608</v>
       </c>
       <c r="C4" t="n">
-        <v>22.26599925597945</v>
+        <v>22.64869534322147</v>
       </c>
       <c r="D4" t="n">
-        <v>25.01739597917714</v>
+        <v>25.42170985137687</v>
       </c>
       <c r="E4" t="n">
-        <v>27.76879270237483</v>
+        <v>28.19472435953228</v>
       </c>
       <c r="F4" t="n">
-        <v>30.52018942557253</v>
+        <v>30.96773886768767</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.2506879640988</v>
+        <v>20.63998666977654</v>
       </c>
       <c r="C5" t="n">
-        <v>23.0020846872965</v>
+        <v>23.41300117793192</v>
       </c>
       <c r="D5" t="n">
-        <v>25.75348141049419</v>
+        <v>26.18601568608732</v>
       </c>
       <c r="E5" t="n">
-        <v>28.50487813369188</v>
+        <v>28.95903019424274</v>
       </c>
       <c r="F5" t="n">
-        <v>31.25627485688958</v>
+        <v>31.73204470239812</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.98677339541585</v>
+        <v>21.404292504487</v>
       </c>
       <c r="C6" t="n">
-        <v>23.73817011861355</v>
+        <v>24.17730701264238</v>
       </c>
       <c r="D6" t="n">
-        <v>26.48956684181124</v>
+        <v>26.95032152079778</v>
       </c>
       <c r="E6" t="n">
-        <v>29.24096356500893</v>
+        <v>29.72333602895319</v>
       </c>
       <c r="F6" t="n">
-        <v>31.99236028820663</v>
+        <v>32.49635053710858</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>24.93</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.02</v>
+        <v>25.42</v>
       </c>
     </row>
   </sheetData>
